--- a/business_forms/050_retail_compliance_assessment_form--business_forms.xlsx
+++ b/business_forms/050_retail_compliance_assessment_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,10 +437,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>store audit</t>
+          <t>Store Audit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>store_number</t>
+          <t>Store Number</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>store name</t>
+          <t>Store Name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>store type</t>
+          <t>Store Type</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>store_type</t>
+          <t>compliance_standards</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>store type</t>
+          <t>Compliance Standards</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compliance_standards</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>compliance standards</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,182 +676,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compliance_standards</t>
+          <t>date_completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>compliance standards</t>
+          <t>Date Completed</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>photos</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>date_completed</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>date completed</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>date_completed</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>date completed</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>time_completed</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>time completed</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -969,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -986,63 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>store_type_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>store_type_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>store_type_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>False</t>
         </is>
       </c>
     </row>
